--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 38926-2026 artfynd.xlsx
+++ b/artfynd/A 38926-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951442</v>
       </c>
       <c r="B2" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136954828</v>
       </c>
       <c r="B3" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>136951440</v>
       </c>
       <c r="B4" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
         <v>136954832</v>
       </c>
       <c r="B5" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
